--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>64.68990342564743</v>
+        <v>10.51210930666771</v>
       </c>
       <c r="D2" t="n">
-        <v>63.40624729344754</v>
+        <v>10.30351518518522</v>
       </c>
       <c r="E2" t="n">
-        <v>12.34822550307454</v>
+        <v>2.006586644249614</v>
       </c>
       <c r="F2" t="n">
-        <v>12.20750169449137</v>
+        <v>1.983719025354847</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.85056819058208</v>
+        <v>9.238217330969588</v>
       </c>
       <c r="D3" t="n">
-        <v>56.00615266610982</v>
+        <v>9.100999808242847</v>
       </c>
       <c r="E3" t="n">
-        <v>12.34822550307454</v>
+        <v>2.006586644249614</v>
       </c>
       <c r="F3" t="n">
-        <v>12.20750169449137</v>
+        <v>1.983719025354847</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>58.56163790347679</v>
+        <v>9.516266159314979</v>
       </c>
       <c r="D4" t="n">
-        <v>58.20068102941099</v>
+        <v>9.457610667279285</v>
       </c>
       <c r="E4" t="n">
-        <v>12.34822550307454</v>
+        <v>2.006586644249614</v>
       </c>
       <c r="F4" t="n">
-        <v>12.20750169449137</v>
+        <v>1.983719025354847</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>66.68428169558277</v>
+        <v>10.8361957755322</v>
       </c>
       <c r="D5" t="n">
-        <v>65.4849915288158</v>
+        <v>10.64131112343257</v>
       </c>
       <c r="E5" t="n">
-        <v>12.34822550307454</v>
+        <v>2.006586644249614</v>
       </c>
       <c r="F5" t="n">
-        <v>12.20750169449137</v>
+        <v>1.983719025354847</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.28658376714247</v>
+        <v>8.496569862160651</v>
       </c>
       <c r="D6" t="n">
-        <v>52.2000509842861</v>
+        <v>8.482508284946492</v>
       </c>
       <c r="E6" t="n">
-        <v>12.34822550307454</v>
+        <v>2.006586644249614</v>
       </c>
       <c r="F6" t="n">
-        <v>12.20750169449137</v>
+        <v>1.983719025354847</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.54766285520972</v>
+        <v>5.93899521397158</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27016471193945</v>
+        <v>5.731401765690161</v>
       </c>
       <c r="E7" t="n">
-        <v>12.34822550307454</v>
+        <v>2.006586644249614</v>
       </c>
       <c r="F7" t="n">
-        <v>12.20750169449137</v>
+        <v>1.983719025354847</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.0725839738297</v>
+        <v>4.724294895747326</v>
       </c>
       <c r="D8" t="n">
-        <v>28.6843206548371</v>
+        <v>4.661202106411029</v>
       </c>
       <c r="E8" t="n">
-        <v>12.34822550307454</v>
+        <v>2.006586644249614</v>
       </c>
       <c r="F8" t="n">
-        <v>12.20750169449137</v>
+        <v>1.983719025354847</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.47488235116298</v>
+        <v>5.764668382063985</v>
       </c>
       <c r="D9" t="n">
-        <v>36.42611248416193</v>
+        <v>5.919243278676313</v>
       </c>
       <c r="E9" t="n">
-        <v>12.34822550307454</v>
+        <v>2.006586644249614</v>
       </c>
       <c r="F9" t="n">
-        <v>12.20750169449137</v>
+        <v>1.983719025354847</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.27553744828414</v>
+        <v>5.082274835346174</v>
       </c>
       <c r="D10" t="n">
-        <v>31.61499318415095</v>
+        <v>5.13743639242453</v>
       </c>
       <c r="E10" t="n">
-        <v>12.34822550307454</v>
+        <v>2.006586644249614</v>
       </c>
       <c r="F10" t="n">
-        <v>12.20750169449137</v>
+        <v>1.983719025354847</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>46.92188833367782</v>
+        <v>7.624806854222646</v>
       </c>
       <c r="D11" t="n">
-        <v>48.03785349833105</v>
+        <v>7.806151193478796</v>
       </c>
       <c r="E11" t="n">
-        <v>12.34822550307454</v>
+        <v>2.006586644249614</v>
       </c>
       <c r="F11" t="n">
-        <v>12.20750169449137</v>
+        <v>1.983719025354847</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>52.00184967380077</v>
+        <v>8.450300571992626</v>
       </c>
       <c r="D12" t="n">
-        <v>52.1438991715719</v>
+        <v>8.473383615380435</v>
       </c>
       <c r="E12" t="n">
-        <v>12.34822550307454</v>
+        <v>2.006586644249614</v>
       </c>
       <c r="F12" t="n">
-        <v>12.20750169449137</v>
+        <v>1.983719025354847</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>62.90067776407487</v>
+        <v>10.22136013666217</v>
       </c>
       <c r="D13" t="n">
-        <v>64.14841533638939</v>
+        <v>10.42411749216328</v>
       </c>
       <c r="E13" t="n">
-        <v>12.34822550307454</v>
+        <v>2.006586644249614</v>
       </c>
       <c r="F13" t="n">
-        <v>12.20750169449137</v>
+        <v>1.983719025354847</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>51.98087766940194</v>
+        <v>8.446892621277815</v>
       </c>
       <c r="D14" t="n">
-        <v>53.09212006546159</v>
+        <v>8.627469510637509</v>
       </c>
       <c r="E14" t="n">
-        <v>12.34822550307454</v>
+        <v>2.006586644249614</v>
       </c>
       <c r="F14" t="n">
-        <v>12.20750169449137</v>
+        <v>1.983719025354847</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
